--- a/Results/Convex_combination/Clustering/n10000/Clustering_Results.xlsx
+++ b/Results/Convex_combination/Clustering/n10000/Clustering_Results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UserA1\Documents\GitHub\Ordinal_Patterns_R\Results\Convex_combination\Clustering\n10000\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B3B3A3-AEFF-483C-BA3E-F50901EBF38F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D890A1F6-B0A0-4ADA-9C1A-B6F9CB47FF04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2160" yWindow="2544" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cluster_Assignments" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1520" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="44">
   <si>
     <t>Class</t>
   </si>
@@ -34,55 +34,52 @@
     <t>ARMA(2,2)</t>
   </si>
   <si>
-    <t>7</t>
+    <t>2</t>
   </si>
   <si>
     <t>AR(2)</t>
   </si>
   <si>
-    <t>5</t>
+    <t>4</t>
   </si>
   <si>
     <t>MA(2)</t>
   </si>
   <si>
-    <t>10</t>
+    <t>9</t>
   </si>
   <si>
     <t>Logistic</t>
   </si>
   <si>
-    <t>8</t>
+    <t>7</t>
   </si>
   <si>
     <t>Sine</t>
   </si>
   <si>
-    <t>12</t>
+    <t>1</t>
   </si>
   <si>
     <t>ARMA+Sine(w=0.1)</t>
   </si>
   <si>
-    <t>9</t>
+    <t>8</t>
   </si>
   <si>
     <t>ARMA+Sine(w=0.2)</t>
   </si>
   <si>
-    <t>6</t>
+    <t>5</t>
   </si>
   <si>
     <t>ARMA+Sine(w=0.3)</t>
   </si>
   <si>
-    <t>1</t>
+    <t>6</t>
   </si>
   <si>
     <t>AR2+Logistic(w=0.1)</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>AR2+Sine(w=0.8)</t>
@@ -91,7 +88,7 @@
     <t>MA2+Logistic(w=0.2)</t>
   </si>
   <si>
-    <t>4</t>
+    <t>3</t>
   </si>
   <si>
     <t>MA2+Logistic(w=0.7)</t>
@@ -100,7 +97,7 @@
     <t>MA2+Sine(w=0.4)</t>
   </si>
   <si>
-    <t>11</t>
+    <t>10</t>
   </si>
   <si>
     <t>MA2+Sine(w=0.6)</t>
@@ -109,7 +106,7 @@
     <t>MA2+Sine(w=0.8)</t>
   </si>
   <si>
-    <t>3</t>
+    <t>11</t>
   </si>
   <si>
     <t>H_Shannon</t>
@@ -146,9 +143,6 @@
   </si>
   <si>
     <t>Var_H_Tsallis</t>
-  </si>
-  <si>
-    <t>Var_H_Fisher</t>
   </si>
   <si>
     <t>Var_C_Shannon</t>
@@ -513,15 +507,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B751"/>
+  <dimension ref="A1:K751"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.5546875" customWidth="1"/>
-    <col min="9" max="9" width="19.88671875" customWidth="1"/>
-    <col min="10" max="10" width="10" customWidth="1"/>
+    <col min="1" max="1" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -529,156 +521,237 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="F3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="F5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7">
+        <v>6</v>
+      </c>
+      <c r="F7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8">
+        <v>7</v>
+      </c>
+      <c r="F8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
         <v>12</v>
       </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="E10">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I10" t="s">
+        <v>25</v>
+      </c>
+      <c r="K10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="E11">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="E12">
+        <v>11</v>
+      </c>
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B19" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B20" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
@@ -691,114 +764,114 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="B27" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B28" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B30" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="B31" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B32" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B33" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B34" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B35" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
@@ -811,114 +884,114 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B37" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B38" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B39" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B40" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B41" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="B42" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B43" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="B44" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B45" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="B46" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B47" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B48" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B49" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B50" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
@@ -931,50 +1004,50 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B52" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B53" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B54" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B55" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B56" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B57" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
@@ -982,119 +1055,119 @@
         <v>23</v>
       </c>
       <c r="B58" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
+        <v>23</v>
+      </c>
+      <c r="B59" t="s">
         <v>24</v>
-      </c>
-      <c r="B59" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B60" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B61" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="B62" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="B63" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="B64" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B65" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="B66" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B67" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B68" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B69" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B70" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B71" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B72" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
@@ -1102,119 +1175,119 @@
         <v>23</v>
       </c>
       <c r="B73" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>23</v>
+      </c>
+      <c r="B74" t="s">
         <v>24</v>
-      </c>
-      <c r="B74" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B75" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B76" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="B77" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="B78" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="B79" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B80" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="B81" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B82" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B83" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B84" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B85" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B86" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B87" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
@@ -1222,191 +1295,191 @@
         <v>23</v>
       </c>
       <c r="B88" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
+        <v>23</v>
+      </c>
+      <c r="B89" t="s">
         <v>24</v>
-      </c>
-      <c r="B89" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B90" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B91" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="B92" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="B93" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="B94" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B95" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="B96" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B97" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B98" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B99" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B100" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B101" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B102" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B103" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B104" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="B105" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
+        <v>12</v>
+      </c>
+      <c r="B106" t="s">
         <v>27</v>
-      </c>
-      <c r="B106" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B107" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B108" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B109" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B110" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B111" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
@@ -1414,199 +1487,199 @@
         <v>12</v>
       </c>
       <c r="B112" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B113" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B114" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B115" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B116" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B117" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B118" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B119" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="B120" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
+        <v>12</v>
+      </c>
+      <c r="B121" t="s">
         <v>27</v>
-      </c>
-      <c r="B121" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B122" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B123" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B124" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B125" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B126" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B127" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B128" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="B129" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="B130" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="B131" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="B132" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="B133" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="B134" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="B135" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="B136" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
@@ -1614,119 +1687,119 @@
         <v>2</v>
       </c>
       <c r="B137" t="s">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B138" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B139" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B140" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B141" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B142" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B143" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="B144" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="B145" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="B146" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="B147" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="B148" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="B149" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="B150" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="B151" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
@@ -1739,114 +1812,114 @@
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B153" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B154" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B155" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B156" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B157" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B158" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="B159" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="B160" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="B161" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="B162" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="B163" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="B164" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="B165" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="B166" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.3">
@@ -1859,186 +1932,186 @@
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B168" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B169" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B170" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B171" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B172" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B173" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="B174" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="B175" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="B176" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
+        <v>20</v>
+      </c>
+      <c r="B177" t="s">
         <v>21</v>
-      </c>
-      <c r="B177" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B178" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B179" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B180" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B181" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B182" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="B183" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B184" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B185" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B186" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B187" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B188" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B189" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B190" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.3">
@@ -2046,119 +2119,119 @@
         <v>20</v>
       </c>
       <c r="B191" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
+        <v>20</v>
+      </c>
+      <c r="B192" t="s">
         <v>21</v>
-      </c>
-      <c r="B192" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B193" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B194" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B195" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B196" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B197" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="B198" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B199" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B200" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B201" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B202" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B203" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B204" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B205" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.3">
@@ -2166,119 +2239,119 @@
         <v>20</v>
       </c>
       <c r="B206" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
+        <v>20</v>
+      </c>
+      <c r="B207" t="s">
         <v>21</v>
-      </c>
-      <c r="B207" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B208" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B209" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B210" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B211" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B212" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="B213" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B214" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B215" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B216" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B217" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B218" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B219" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B220" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.3">
@@ -2286,60 +2359,60 @@
         <v>20</v>
       </c>
       <c r="B221" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
+        <v>20</v>
+      </c>
+      <c r="B222" t="s">
         <v>21</v>
-      </c>
-      <c r="B222" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B223" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B224" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B225" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B226" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B227" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B228" t="s">
         <v>5</v>
@@ -2347,63 +2420,63 @@
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B229" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B230" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B231" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B232" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B233" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B234" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="B235" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B236" t="s">
         <v>5</v>
@@ -2411,50 +2484,50 @@
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B237" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B238" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="B239" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B240" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="B241" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="B242" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.3">
@@ -2467,63 +2540,63 @@
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B244" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B245" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B246" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B247" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B248" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="B249" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B250" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B251" t="s">
         <v>5</v>
@@ -2531,55 +2604,55 @@
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B252" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="B253" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B254" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="B255" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B256" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B257" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B258" t="s">
         <v>5</v>
@@ -2587,63 +2660,63 @@
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B259" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B260" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B261" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B262" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B263" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B264" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="B265" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B266" t="s">
         <v>5</v>
@@ -2651,50 +2724,50 @@
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B267" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B268" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="B269" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B270" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="B271" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="B272" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.3">
@@ -2707,63 +2780,63 @@
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B274" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B275" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B276" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B277" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B278" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="B279" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B280" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B281" t="s">
         <v>5</v>
@@ -2771,55 +2844,55 @@
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B282" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="B283" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B284" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="B285" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B286" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B287" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B288" t="s">
         <v>5</v>
@@ -2827,63 +2900,63 @@
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B289" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B290" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B291" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B292" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B293" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B294" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="B295" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B296" t="s">
         <v>5</v>
@@ -2891,50 +2964,50 @@
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B297" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B298" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="B299" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B300" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="B301" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="B302" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.3">
@@ -2947,63 +3020,63 @@
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B304" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B305" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B306" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B307" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B308" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="B309" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B310" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B311" t="s">
         <v>5</v>
@@ -3011,55 +3084,55 @@
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B312" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="B313" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B314" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="B315" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B316" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B317" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B318" t="s">
         <v>5</v>
@@ -3067,63 +3140,63 @@
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B319" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B320" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B321" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B322" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B323" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B324" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="B325" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B326" t="s">
         <v>5</v>
@@ -3131,90 +3204,90 @@
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B327" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B328" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B329" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="B330" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="B331" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B332" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B333" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B334" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B335" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B336" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B337" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.3">
@@ -3227,114 +3300,114 @@
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B339" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B340" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B341" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B342" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B343" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B344" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="B345" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="B346" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B347" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B348" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B349" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B350" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B351" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B352" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.3">
@@ -3347,114 +3420,114 @@
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B354" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B355" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B356" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B357" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B358" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B359" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="B360" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="B361" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B362" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B363" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B364" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B365" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B366" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B367" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.3">
@@ -3467,122 +3540,122 @@
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B369" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B370" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B371" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B372" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B373" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B374" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="B375" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="B376" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B377" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B378" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B379" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B380" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B381" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B382" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B383" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.3">
@@ -3595,114 +3668,114 @@
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B385" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B386" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B387" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B388" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B389" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="B390" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B391" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B392" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B393" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B394" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B395" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B396" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B397" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B398" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.3">
@@ -3715,114 +3788,114 @@
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B400" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B401" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B402" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B403" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B404" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="B405" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B406" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B407" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B408" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B409" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B410" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B411" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B412" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B413" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.3">
@@ -3835,122 +3908,122 @@
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B415" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B416" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B417" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B418" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B419" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="B420" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B421" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B422" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B423" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B424" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B425" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B426" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B427" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B428" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B429" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.3">
@@ -3958,84 +4031,84 @@
         <v>18</v>
       </c>
       <c r="B430" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B431" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B432" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="B433" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B434" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="B435" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B436" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B437" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="B438" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B439" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B440" t="s">
         <v>9</v>
@@ -4043,114 +4116,114 @@
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B441" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B442" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B443" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B444" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B445" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B446" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="B447" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B448" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="B449" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B450" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="B451" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="B452" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B453" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="B454" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.3">
@@ -4163,34 +4236,34 @@
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B456" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B457" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B458" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B459" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.3">
@@ -4198,84 +4271,84 @@
         <v>18</v>
       </c>
       <c r="B460" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B461" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B462" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="B463" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B464" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="B465" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B466" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B467" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="B468" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B469" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B470" t="s">
         <v>9</v>
@@ -4283,114 +4356,114 @@
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B471" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B472" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B473" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B474" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B475" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B476" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="B477" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B478" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="B479" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B480" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="B481" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="B482" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B483" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="B484" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.3">
@@ -4403,34 +4476,34 @@
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B486" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B487" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B488" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B489" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.3">
@@ -4438,84 +4511,84 @@
         <v>18</v>
       </c>
       <c r="B490" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B491" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B492" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="B493" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B494" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="B495" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B496" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B497" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="B498" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B499" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B500" t="s">
         <v>9</v>
@@ -4523,114 +4596,114 @@
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B501" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B502" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B503" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B504" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B505" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B506" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="B507" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B508" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="B509" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B510" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="B511" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="B512" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B513" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="B514" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.3">
@@ -4643,34 +4716,34 @@
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B516" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B517" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B518" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B519" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.3">
@@ -4678,95 +4751,95 @@
         <v>18</v>
       </c>
       <c r="B520" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B521" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B522" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="B523" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B524" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="B525" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B526" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B527" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A528" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B528" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B529" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B530" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B531" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.3">
@@ -4779,114 +4852,114 @@
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A533" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B533" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A534" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B534" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B535" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B536" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B537" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B538" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B539" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="B540" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B541" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B542" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B543" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B544" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B545" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B546" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.3">
@@ -4899,47 +4972,47 @@
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B548" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B549" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B550" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B551" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B552" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B553" t="s">
         <v>7</v>
@@ -4947,10 +5020,10 @@
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B554" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.3">
@@ -4963,7 +5036,7 @@
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="B556" t="s">
         <v>7</v>
@@ -4971,23 +5044,23 @@
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="B557" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="B558" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="B559" t="s">
         <v>7</v>
@@ -4995,71 +5068,71 @@
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B560" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B561" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A562" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="B562" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B563" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B564" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A565" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B565" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A566" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B566" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A567" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B567" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A568" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="B568" t="s">
         <v>7</v>
@@ -5067,15 +5140,15 @@
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B569" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B570" t="s">
         <v>7</v>
@@ -5083,7 +5156,7 @@
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B571" t="s">
         <v>7</v>
@@ -5091,23 +5164,23 @@
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B572" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="B573" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="B574" t="s">
         <v>7</v>
@@ -5115,71 +5188,71 @@
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="B575" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B576" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A577" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B577" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A578" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B578" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A579" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B579" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="B580" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B581" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A582" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B582" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A583" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B583" t="s">
         <v>7</v>
@@ -5187,15 +5260,15 @@
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A584" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="B584" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A585" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B585" t="s">
         <v>7</v>
@@ -5203,7 +5276,7 @@
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A586" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B586" t="s">
         <v>7</v>
@@ -5211,23 +5284,23 @@
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A587" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="B587" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A588" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B588" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A589" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B589" t="s">
         <v>7</v>
@@ -5235,71 +5308,71 @@
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A590" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B590" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A591" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="B591" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A592" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B592" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A593" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B593" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A594" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B594" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A595" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B595" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A596" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B596" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A597" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B597" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A598" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B598" t="s">
         <v>7</v>
@@ -5307,15 +5380,15 @@
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B599" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A600" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="B600" t="s">
         <v>7</v>
@@ -5323,7 +5396,7 @@
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A601" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B601" t="s">
         <v>7</v>
@@ -5331,18 +5404,18 @@
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A602" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="B602" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A603" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="B603" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.3">
@@ -5355,71 +5428,71 @@
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A605" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B605" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A606" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B606" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A607" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="B607" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A608" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B608" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A609" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B609" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A610" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B610" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B611" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A612" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B612" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="613" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A613" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B613" t="s">
         <v>7</v>
@@ -5427,10 +5500,10 @@
     </row>
     <row r="614" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B614" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.3">
@@ -5443,7 +5516,7 @@
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A616" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="B616" t="s">
         <v>7</v>
@@ -5451,23 +5524,23 @@
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A617" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="B617" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A618" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="B618" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="619" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A619" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="B619" t="s">
         <v>7</v>
@@ -5475,71 +5548,71 @@
     </row>
     <row r="620" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A620" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B620" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="621" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A621" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B621" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="622" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A622" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="B622" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="623" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A623" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B623" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="624" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A624" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B624" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="625" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A625" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B625" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="626" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A626" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B626" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="627" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A627" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B627" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="628" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A628" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="B628" t="s">
         <v>7</v>
@@ -5547,15 +5620,15 @@
     </row>
     <row r="629" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A629" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B629" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="630" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A630" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B630" t="s">
         <v>7</v>
@@ -5563,7 +5636,7 @@
     </row>
     <row r="631" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A631" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B631" t="s">
         <v>7</v>
@@ -5571,23 +5644,23 @@
     </row>
     <row r="632" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A632" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B632" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="633" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A633" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="B633" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="634" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A634" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="B634" t="s">
         <v>7</v>
@@ -5595,71 +5668,71 @@
     </row>
     <row r="635" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A635" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="B635" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="636" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A636" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B636" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="637" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A637" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B637" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="638" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A638" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B638" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="639" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A639" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B639" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="640" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A640" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="B640" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="641" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A641" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B641" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="642" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A642" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B642" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="643" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A643" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B643" t="s">
         <v>7</v>
@@ -5667,15 +5740,15 @@
     </row>
     <row r="644" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A644" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="B644" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="645" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A645" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B645" t="s">
         <v>7</v>
@@ -5683,7 +5756,7 @@
     </row>
     <row r="646" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A646" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B646" t="s">
         <v>7</v>
@@ -5691,23 +5764,23 @@
     </row>
     <row r="647" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A647" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="B647" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="648" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A648" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B648" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="649" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A649" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B649" t="s">
         <v>7</v>
@@ -5715,71 +5788,71 @@
     </row>
     <row r="650" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A650" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B650" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="651" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A651" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="B651" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A652" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B652" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="653" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A653" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B653" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="654" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A654" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B654" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="655" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A655" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B655" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="656" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A656" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B656" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="657" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A657" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B657" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="658" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A658" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B658" t="s">
         <v>7</v>
@@ -5787,15 +5860,15 @@
     </row>
     <row r="659" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A659" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B659" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="660" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A660" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="B660" t="s">
         <v>7</v>
@@ -5803,7 +5876,7 @@
     </row>
     <row r="661" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A661" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B661" t="s">
         <v>7</v>
@@ -5811,18 +5884,18 @@
     </row>
     <row r="662" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A662" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="B662" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="663" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A663" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="B663" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="664" spans="1:2" x14ac:dyDescent="0.3">
@@ -5835,71 +5908,71 @@
     </row>
     <row r="665" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A665" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B665" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="666" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A666" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B666" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="667" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A667" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="B667" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="668" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A668" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B668" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="669" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A669" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B669" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="670" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A670" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B670" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="671" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A671" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B671" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="672" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A672" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B672" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="673" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A673" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B673" t="s">
         <v>7</v>
@@ -5907,10 +5980,10 @@
     </row>
     <row r="674" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A674" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B674" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="675" spans="1:2" x14ac:dyDescent="0.3">
@@ -5923,7 +5996,7 @@
     </row>
     <row r="676" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A676" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="B676" t="s">
         <v>7</v>
@@ -5931,23 +6004,23 @@
     </row>
     <row r="677" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A677" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="B677" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="678" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A678" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="B678" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="679" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A679" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="B679" t="s">
         <v>7</v>
@@ -5955,71 +6028,71 @@
     </row>
     <row r="680" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A680" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B680" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="681" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A681" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B681" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="682" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A682" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="B682" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="683" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A683" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B683" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="684" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A684" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B684" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="685" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A685" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B685" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="686" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A686" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B686" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="687" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A687" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B687" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="688" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A688" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="B688" t="s">
         <v>7</v>
@@ -6027,15 +6100,15 @@
     </row>
     <row r="689" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A689" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B689" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="690" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A690" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B690" t="s">
         <v>7</v>
@@ -6043,7 +6116,7 @@
     </row>
     <row r="691" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A691" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B691" t="s">
         <v>7</v>
@@ -6051,23 +6124,23 @@
     </row>
     <row r="692" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A692" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B692" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="693" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A693" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="B693" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="694" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A694" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="B694" t="s">
         <v>7</v>
@@ -6075,71 +6148,71 @@
     </row>
     <row r="695" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A695" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="B695" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="696" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A696" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B696" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="697" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A697" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B697" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="698" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A698" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B698" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="699" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A699" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B699" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="700" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A700" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="B700" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="701" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A701" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B701" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="702" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A702" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B702" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="703" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A703" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B703" t="s">
         <v>7</v>
@@ -6147,15 +6220,15 @@
     </row>
     <row r="704" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A704" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="B704" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="705" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A705" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B705" t="s">
         <v>7</v>
@@ -6163,7 +6236,7 @@
     </row>
     <row r="706" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A706" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B706" t="s">
         <v>7</v>
@@ -6171,23 +6244,23 @@
     </row>
     <row r="707" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A707" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="B707" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="708" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A708" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B708" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="709" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A709" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B709" t="s">
         <v>7</v>
@@ -6195,71 +6268,71 @@
     </row>
     <row r="710" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A710" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B710" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="711" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A711" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="B711" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="712" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A712" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B712" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="713" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A713" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B713" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="714" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A714" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B714" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="715" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A715" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B715" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="716" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A716" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B716" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="717" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A717" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B717" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="718" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A718" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B718" t="s">
         <v>7</v>
@@ -6267,15 +6340,15 @@
     </row>
     <row r="719" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A719" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B719" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="720" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A720" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="B720" t="s">
         <v>7</v>
@@ -6283,7 +6356,7 @@
     </row>
     <row r="721" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A721" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B721" t="s">
         <v>7</v>
@@ -6291,18 +6364,18 @@
     </row>
     <row r="722" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A722" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="B722" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="723" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A723" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="B723" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="724" spans="1:2" x14ac:dyDescent="0.3">
@@ -6315,71 +6388,71 @@
     </row>
     <row r="725" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A725" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B725" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="726" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A726" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B726" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="727" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A727" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="B727" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="728" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A728" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B728" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="729" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A729" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B729" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="730" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A730" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B730" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="731" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A731" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B731" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="732" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A732" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B732" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="733" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A733" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B733" t="s">
         <v>7</v>
@@ -6387,10 +6460,10 @@
     </row>
     <row r="734" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A734" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B734" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="735" spans="1:2" x14ac:dyDescent="0.3">
@@ -6403,7 +6476,7 @@
     </row>
     <row r="736" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A736" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="B736" t="s">
         <v>7</v>
@@ -6411,23 +6484,23 @@
     </row>
     <row r="737" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A737" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="B737" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="738" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A738" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="B738" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="739" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A739" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="B739" t="s">
         <v>7</v>
@@ -6435,71 +6508,71 @@
     </row>
     <row r="740" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A740" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B740" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="741" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A741" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B741" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="742" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A742" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="B742" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="743" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A743" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B743" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="744" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A744" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B744" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="745" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A745" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B745" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="746" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A746" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B746" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="747" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A747" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B747" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="748" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A748" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="B748" t="s">
         <v>7</v>
@@ -6507,15 +6580,15 @@
     </row>
     <row r="749" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A749" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B749" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="750" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A750" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B750" t="s">
         <v>7</v>
@@ -6523,592 +6596,515 @@
     </row>
     <row r="751" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A751" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B751" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B751">
+    <sortCondition ref="B1:B751"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2">
+        <v>-2.1436561098486111</v>
+      </c>
+      <c r="B2">
+        <v>-1.96547707184287</v>
+      </c>
+      <c r="C2">
+        <v>-2.2913709207694248</v>
+      </c>
+      <c r="D2">
+        <v>0.48981595642554399</v>
+      </c>
+      <c r="E2">
+        <v>0.93528588916528521</v>
+      </c>
+      <c r="F2">
+        <v>0.84298985476453292</v>
+      </c>
+      <c r="G2">
+        <v>1.2516867792886559</v>
+      </c>
+      <c r="H2">
+        <v>1.4504562415499009</v>
+      </c>
+      <c r="I2">
+        <v>2.017940821393704</v>
+      </c>
+      <c r="J2">
+        <v>-0.48918121438880408</v>
+      </c>
+      <c r="K2">
+        <v>0.1865034712441444</v>
+      </c>
+      <c r="L2">
+        <v>0.17018251253687131</v>
+      </c>
+      <c r="M2">
+        <v>-0.86785632563250981</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>0.10162757740831969</v>
+      </c>
+      <c r="B3">
+        <v>4.7657879332861433E-2</v>
+      </c>
+      <c r="C3">
+        <v>0.19156533184197369</v>
+      </c>
+      <c r="D3">
+        <v>0.79598662614564519</v>
+      </c>
+      <c r="E3">
+        <v>0.33588433089758718</v>
+      </c>
+      <c r="F3">
+        <v>0.37376128034807182</v>
+      </c>
+      <c r="G3">
+        <v>0.201822244080232</v>
+      </c>
+      <c r="H3">
+        <v>6.2572347950706181E-2</v>
+      </c>
+      <c r="I3">
+        <v>-3.8588169380526678E-2</v>
+      </c>
+      <c r="J3">
+        <v>0.39838738725791811</v>
+      </c>
+      <c r="K3">
+        <v>-0.13679563597369149</v>
+      </c>
+      <c r="L3">
+        <v>-0.15169438136820981</v>
+      </c>
+      <c r="M3">
+        <v>1.055646216150532</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>-0.3620683639961414</v>
+      </c>
+      <c r="B4">
+        <v>-0.36373868724420638</v>
+      </c>
+      <c r="C4">
+        <v>-0.196892057022718</v>
+      </c>
+      <c r="D4">
+        <v>1.1305129478023841</v>
+      </c>
+      <c r="E4">
+        <v>0.86201191316813519</v>
+      </c>
+      <c r="F4">
+        <v>0.89752040809651978</v>
+      </c>
+      <c r="G4">
+        <v>0.76313312431132485</v>
+      </c>
+      <c r="H4">
+        <v>0.73420459645828184</v>
+      </c>
+      <c r="I4">
+        <v>0.48111963543658531</v>
+      </c>
+      <c r="J4">
+        <v>0.1072421915129641</v>
+      </c>
+      <c r="K4">
+        <v>-0.34133161203391138</v>
+      </c>
+      <c r="L4">
+        <v>-0.36078367784165549</v>
+      </c>
+      <c r="M4">
+        <v>-0.10129423858538331</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>0.46371127229121217</v>
+      </c>
+      <c r="B5">
+        <v>0.41276952737464168</v>
+      </c>
+      <c r="C5">
+        <v>0.49567849101915012</v>
+      </c>
+      <c r="D5">
+        <v>0.42550805380696921</v>
+      </c>
+      <c r="E5">
+        <v>-0.18791500046952189</v>
+      </c>
+      <c r="F5">
+        <v>-0.14028612525281131</v>
+      </c>
+      <c r="G5">
+        <v>-0.29007414385348468</v>
+      </c>
+      <c r="H5">
+        <v>-0.39841969169174252</v>
+      </c>
+      <c r="I5">
+        <v>-0.43892297293867338</v>
+      </c>
+      <c r="J5">
+        <v>0.36540069789607071</v>
+      </c>
+      <c r="K5">
+        <v>-0.1681350178557304</v>
+      </c>
+      <c r="L5">
+        <v>-0.18706331182710781</v>
+      </c>
+      <c r="M5">
+        <v>1.9312053015261861</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>-0.57329387445538083</v>
+      </c>
+      <c r="B6">
+        <v>-0.84903144403962183</v>
+      </c>
+      <c r="C6">
+        <v>-0.72651809117504995</v>
+      </c>
+      <c r="D6">
+        <v>-0.2355568290487681</v>
+      </c>
+      <c r="E6">
+        <v>0.57850636476593575</v>
+      </c>
+      <c r="F6">
+        <v>0.39432861063314861</v>
+      </c>
+      <c r="G6">
+        <v>0.43134709014579647</v>
+      </c>
+      <c r="H6">
+        <v>-0.23337974282704141</v>
+      </c>
+      <c r="I6">
+        <v>0.36907544005734172</v>
+      </c>
+      <c r="J6">
+        <v>2.31727020401331</v>
+      </c>
+      <c r="K6">
+        <v>2.7092761284931401</v>
+      </c>
+      <c r="L6">
+        <v>2.7175667334416751</v>
+      </c>
+      <c r="M6">
+        <v>5.0543211572879949E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7">
         <v>8.5144137215363775E-4</v>
       </c>
-      <c r="B2">
+      <c r="B7">
         <v>-0.13513297536918489</v>
       </c>
-      <c r="C2">
+      <c r="C7">
         <v>2.3988247956714621E-2</v>
       </c>
-      <c r="D2">
-        <v>-0.23342520141572659</v>
-      </c>
-      <c r="E2">
+      <c r="D7">
+        <v>-5.2569058805918147E-2</v>
+      </c>
+      <c r="E7">
         <v>0.33357211389581931</v>
       </c>
-      <c r="F2">
+      <c r="F7">
         <v>0.31835585831235308</v>
       </c>
-      <c r="G2">
+      <c r="G7">
         <v>0.19374075729945431</v>
       </c>
-      <c r="H2">
-        <v>-0.40821203450834692</v>
-      </c>
-      <c r="I2">
+      <c r="H7">
+        <v>-0.32409961727772812</v>
+      </c>
+      <c r="I7">
         <v>-1.057938281472319E-2</v>
       </c>
-      <c r="J2">
+      <c r="J7">
         <v>0.38606082329794278</v>
       </c>
-      <c r="K2">
+      <c r="K7">
         <v>0.57054931568523781</v>
       </c>
-      <c r="L2">
+      <c r="L7">
         <v>0.5641096629753023</v>
       </c>
-      <c r="M2">
-        <v>-0.27975078009488791</v>
-      </c>
-      <c r="N2">
+      <c r="M7">
         <v>0.35827420780262909</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>-0.74990006940638199</v>
-      </c>
-      <c r="B3">
-        <v>-0.63030796236900632</v>
-      </c>
-      <c r="C3">
-        <v>-0.4766324898050614</v>
-      </c>
-      <c r="D3">
-        <v>1.5545423666520259</v>
-      </c>
-      <c r="E3">
-        <v>1.246457421458435</v>
-      </c>
-      <c r="F3">
-        <v>1.3469410534677031</v>
-      </c>
-      <c r="G3">
-        <v>1.260298537462718</v>
-      </c>
-      <c r="H3">
-        <v>1.4134891011719519</v>
-      </c>
-      <c r="I3">
-        <v>0.9752900361025364</v>
-      </c>
-      <c r="J3">
-        <v>-0.30648048975559028</v>
-      </c>
-      <c r="K3">
-        <v>-0.62154369231744111</v>
-      </c>
-      <c r="L3">
-        <v>-0.53924082050752764</v>
-      </c>
-      <c r="M3">
-        <v>1.2444944271794149</v>
-      </c>
-      <c r="N3">
-        <v>-0.69858458458180239</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>9.2619412020523345E-2</v>
-      </c>
-      <c r="B4">
-        <v>4.0669195226574487E-2</v>
-      </c>
-      <c r="C4">
-        <v>0.1853737493492334</v>
-      </c>
-      <c r="D4">
-        <v>0.43300319071505289</v>
-      </c>
-      <c r="E4">
-        <v>0.35028573938918672</v>
-      </c>
-      <c r="F4">
-        <v>0.38879397086124873</v>
-      </c>
-      <c r="G4">
-        <v>0.21611675010264311</v>
-      </c>
-      <c r="H4">
-        <v>-0.1087430185613235</v>
-      </c>
-      <c r="I4">
-        <v>-2.6871782683990191E-2</v>
-      </c>
-      <c r="J4">
-        <v>0.35205385005151502</v>
-      </c>
-      <c r="K4">
-        <v>-0.13377225825248051</v>
-      </c>
-      <c r="L4">
-        <v>-0.18760284179859149</v>
-      </c>
-      <c r="M4">
-        <v>1.6926841578023051</v>
-      </c>
-      <c r="N4">
-        <v>0.97460042334857777</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>-0.3620683639961414</v>
-      </c>
-      <c r="B5">
-        <v>-0.36373868724420638</v>
-      </c>
-      <c r="C5">
-        <v>-0.196892057022718</v>
-      </c>
-      <c r="D5">
-        <v>0.97076855904470871</v>
-      </c>
-      <c r="E5">
-        <v>0.86201191316813519</v>
-      </c>
-      <c r="F5">
-        <v>0.89752040809651978</v>
-      </c>
-      <c r="G5">
-        <v>0.76313312431132485</v>
-      </c>
-      <c r="H5">
-        <v>0.54127722660645683</v>
-      </c>
-      <c r="I5">
-        <v>0.48111963543658531</v>
-      </c>
-      <c r="J5">
-        <v>0.1072421915129641</v>
-      </c>
-      <c r="K5">
-        <v>-0.34133161203391138</v>
-      </c>
-      <c r="L5">
-        <v>-0.36078367784165549</v>
-      </c>
-      <c r="M5">
-        <v>1.132880374208407</v>
-      </c>
-      <c r="N5">
-        <v>-0.10129423858538331</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>0.46371127229121217</v>
-      </c>
-      <c r="B6">
-        <v>0.41276952737464168</v>
-      </c>
-      <c r="C6">
-        <v>0.49567849101915012</v>
-      </c>
-      <c r="D6">
-        <v>5.7022249375964007E-2</v>
-      </c>
-      <c r="E6">
-        <v>-0.18791500046952189</v>
-      </c>
-      <c r="F6">
-        <v>-0.14028612525281131</v>
-      </c>
-      <c r="G6">
-        <v>-0.29007414385348468</v>
-      </c>
-      <c r="H6">
-        <v>-0.46936287412248162</v>
-      </c>
-      <c r="I6">
-        <v>-0.43892297293867338</v>
-      </c>
-      <c r="J6">
-        <v>0.36540069789607071</v>
-      </c>
-      <c r="K6">
-        <v>-0.1681350178557304</v>
-      </c>
-      <c r="L6">
-        <v>-0.18706331182710781</v>
-      </c>
-      <c r="M6">
-        <v>1.402676283024485</v>
-      </c>
-      <c r="N6">
-        <v>1.9312053015261861</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>-0.57329387445538083</v>
-      </c>
-      <c r="B7">
-        <v>-0.84903144403962183</v>
-      </c>
-      <c r="C7">
-        <v>-0.72651809117504995</v>
-      </c>
-      <c r="D7">
-        <v>-0.35240678966154437</v>
-      </c>
-      <c r="E7">
-        <v>0.57850636476593575</v>
-      </c>
-      <c r="F7">
-        <v>0.39432861063314861</v>
-      </c>
-      <c r="G7">
-        <v>0.43134709014579647</v>
-      </c>
-      <c r="H7">
-        <v>-0.34323951372208578</v>
-      </c>
-      <c r="I7">
-        <v>0.36907544005734172</v>
-      </c>
-      <c r="J7">
-        <v>2.31727020401331</v>
-      </c>
-      <c r="K7">
-        <v>2.7092761284931401</v>
-      </c>
-      <c r="L7">
-        <v>2.7175667334416751</v>
-      </c>
-      <c r="M7">
-        <v>-0.60155115974724616</v>
-      </c>
-      <c r="N7">
-        <v>5.0543211572879949E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>0.11309251517460581</v>
+        <v>-0.89074424734822988</v>
       </c>
       <c r="B8">
-        <v>5.655256819540843E-2</v>
+        <v>-0.70403246525783569</v>
       </c>
       <c r="C8">
-        <v>0.19944552774182489</v>
+        <v>-0.55918256361382079</v>
       </c>
       <c r="D8">
-        <v>0.39899419135398068</v>
+        <v>1.546261670348662</v>
       </c>
       <c r="E8">
-        <v>0.31755526554464231</v>
+        <v>1.374367959538433</v>
       </c>
       <c r="F8">
-        <v>0.35462876514948299</v>
+        <v>1.5338322133114699</v>
       </c>
       <c r="G8">
-        <v>0.18362923641534529</v>
+        <v>1.4643377653492951</v>
       </c>
       <c r="H8">
-        <v>-0.14015550636888319</v>
+        <v>1.821095731057883</v>
       </c>
       <c r="I8">
-        <v>-5.3499934267027663E-2</v>
+        <v>1.181249033668941</v>
       </c>
       <c r="J8">
-        <v>0.45735734370243131</v>
+        <v>-0.6944762956946261</v>
       </c>
       <c r="K8">
-        <v>-0.14064357125523269</v>
+        <v>-0.74852417046319064</v>
       </c>
       <c r="L8">
-        <v>-0.105992704456815</v>
+        <v>-0.64200023959777608</v>
       </c>
       <c r="M8">
-        <v>1.7326137031391791</v>
-      </c>
-      <c r="N8">
-        <v>1.1587954069893831</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+        <v>-0.91351409594475286</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>-1.031588425290076</v>
+        <v>-1.3983112573540251</v>
       </c>
       <c r="B9">
-        <v>-0.77775696814666473</v>
+        <v>-1.590274537594925</v>
       </c>
       <c r="C9">
-        <v>-0.64173263742258124</v>
+        <v>-1.7025933106572071</v>
       </c>
       <c r="D9">
-        <v>2.216460003617839</v>
+        <v>1.8553604109808899E-2</v>
       </c>
       <c r="E9">
-        <v>1.50227849761843</v>
+        <v>0.81074355259713782</v>
       </c>
       <c r="F9">
-        <v>1.7207233731552369</v>
+        <v>0.49924873447563672</v>
       </c>
       <c r="G9">
-        <v>1.6683769932358721</v>
+        <v>0.74679429026528565</v>
       </c>
       <c r="H9">
-        <v>2.4709486443692179</v>
+        <v>0.31595198101771349</v>
       </c>
       <c r="I9">
-        <v>1.3872080312353441</v>
+        <v>1.0568205150790571</v>
       </c>
       <c r="J9">
-        <v>-1.082472101633662</v>
+        <v>2.0679755410230829</v>
       </c>
       <c r="K9">
-        <v>-0.87550464860894095</v>
+        <v>2.071213257807579</v>
       </c>
       <c r="L9">
-        <v>-0.74475965868802452</v>
+        <v>2.085397560480363</v>
       </c>
       <c r="M9">
-        <v>-0.95088645172770248</v>
-      </c>
-      <c r="N9">
-        <v>-1.128443607307704</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+        <v>-0.9841359010862486</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>-1.453075083567583</v>
+        <v>1.129593497480071</v>
       </c>
       <c r="B10">
-        <v>-1.6270769292180061</v>
+        <v>1.1910026152381821</v>
       </c>
       <c r="C10">
-        <v>-1.757650563163321</v>
+        <v>1.0407606379310019</v>
       </c>
       <c r="D10">
-        <v>-6.2493517952824151E-2</v>
+        <v>-1.2700891469461351</v>
       </c>
       <c r="E10">
-        <v>0.82275932466700552</v>
+        <v>-1.377008359531781</v>
       </c>
       <c r="F10">
-        <v>0.51295017295582701</v>
+        <v>-1.3579241037011971</v>
       </c>
       <c r="G10">
-        <v>0.77301295433861705</v>
+        <v>-1.2986636856290039</v>
       </c>
       <c r="H10">
-        <v>0.1451761490028049</v>
+        <v>-0.99728322092946586</v>
       </c>
       <c r="I10">
-        <v>1.114386324725698</v>
+        <v>-1.1566364102582201</v>
       </c>
       <c r="J10">
-        <v>1.909387432710804</v>
+        <v>-0.94603700338365504</v>
       </c>
       <c r="K10">
-        <v>1.9121785606801629</v>
+        <v>-0.70457368813945676</v>
       </c>
       <c r="L10">
-        <v>1.9335548453101139</v>
+        <v>-0.73116443406883069</v>
       </c>
       <c r="M10">
-        <v>-0.38747229211013878</v>
-      </c>
-      <c r="N10">
-        <v>-1.0053572743642609</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+        <v>-0.60006553730361489</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>1.129593497480071</v>
+        <v>0.76530637328099926</v>
       </c>
       <c r="B11">
-        <v>1.1910026152381821</v>
+        <v>0.71131464319468862</v>
       </c>
       <c r="C11">
-        <v>1.0407606379310019</v>
+        <v>0.72084364579716231</v>
       </c>
       <c r="D11">
-        <v>-1.1005363097155729</v>
+        <v>-1.046831304457353</v>
       </c>
       <c r="E11">
-        <v>-1.377008359531781</v>
+        <v>-0.73289241657046278</v>
       </c>
       <c r="F11">
-        <v>-1.3579241037011971</v>
+        <v>-0.69530194642298471</v>
       </c>
       <c r="G11">
-        <v>-1.2986636856290039</v>
+        <v>-0.76861544993969177</v>
       </c>
       <c r="H11">
-        <v>-0.8560815372956424</v>
+        <v>-0.92894640868231104</v>
       </c>
       <c r="I11">
-        <v>-1.1566364102582201</v>
+        <v>-0.79146114984573335</v>
       </c>
       <c r="J11">
-        <v>-0.94603700338365504</v>
+        <v>-0.18686761527240409</v>
       </c>
       <c r="K11">
-        <v>-0.70457368813945676</v>
+        <v>-0.24876709889941001</v>
       </c>
       <c r="L11">
-        <v>-0.73116443406883069</v>
+        <v>-0.29015085592900758</v>
       </c>
       <c r="M11">
-        <v>-0.80134136287353064</v>
-      </c>
-      <c r="N11">
-        <v>-0.60006553730361489</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+        <v>0.87492394110770899</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>0.76530637328099926</v>
+        <v>-1.5078389097811411</v>
       </c>
       <c r="B12">
-        <v>0.71131464319468862</v>
+        <v>-1.663879320841088</v>
       </c>
       <c r="C12">
-        <v>0.72084364579716231</v>
+        <v>-1.8127078156694361</v>
       </c>
       <c r="D12">
-        <v>-0.95979413187844809</v>
+        <v>9.2363998713674164E-2</v>
       </c>
       <c r="E12">
-        <v>-0.73289241657046278</v>
+        <v>0.83477509673687278</v>
       </c>
       <c r="F12">
-        <v>-0.69530194642298471</v>
+        <v>0.52665161143601746</v>
       </c>
       <c r="G12">
-        <v>-0.76861544993969177</v>
+        <v>0.79923161841194845</v>
       </c>
       <c r="H12">
-        <v>-0.81623701450390906</v>
+        <v>0.449994794609826</v>
       </c>
       <c r="I12">
-        <v>-0.79146114984573335</v>
+        <v>1.17195213437234</v>
       </c>
       <c r="J12">
-        <v>-0.18686761527240409</v>
+        <v>1.750799324398526</v>
       </c>
       <c r="K12">
-        <v>-0.24876709889941001</v>
+        <v>1.753143863552747</v>
       </c>
       <c r="L12">
-        <v>-0.29015085592900758</v>
+        <v>1.781712130139866</v>
       </c>
       <c r="M12">
-        <v>-0.79260849124017652</v>
-      </c>
-      <c r="N12">
-        <v>0.87492394110770899</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>-2.1436561098486111</v>
-      </c>
-      <c r="B13">
-        <v>-1.96547707184287</v>
-      </c>
-      <c r="C13">
-        <v>-2.2913709207694248</v>
-      </c>
-      <c r="D13">
-        <v>0.7364102207081541</v>
-      </c>
-      <c r="E13">
-        <v>0.93528588916528521</v>
-      </c>
-      <c r="F13">
-        <v>0.84298985476453292</v>
-      </c>
-      <c r="G13">
-        <v>1.2516867792886559</v>
-      </c>
-      <c r="H13">
-        <v>1.482413852208091</v>
-      </c>
-      <c r="I13">
-        <v>2.017940821393704</v>
-      </c>
-      <c r="J13">
-        <v>-0.48918121438880408</v>
-      </c>
-      <c r="K13">
-        <v>0.1865034712441444</v>
-      </c>
-      <c r="L13">
-        <v>0.17018251253687131</v>
-      </c>
-      <c r="M13">
-        <v>-0.67534589877304929</v>
-      </c>
-      <c r="N13">
-        <v>-0.86785632563250981</v>
+        <v>-1.026578647642272</v>
       </c>
     </row>
   </sheetData>
@@ -7123,10 +7119,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -7134,7 +7130,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>0.4471967967390435</v>
+        <v>0.47713911511536489</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -7142,7 +7138,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.50429005494747736</v>
+        <v>0.52199398270355102</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -7150,7 +7146,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.61417920058500253</v>
+        <v>0.63018835880176294</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -7158,7 +7154,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.63912806465017147</v>
+        <v>0.66589469672690993</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -7166,7 +7162,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0.65871210704179906</v>
+        <v>0.60691774551482502</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -7174,7 +7170,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>0.6726478667869481</v>
+        <v>0.66289592566399669</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -7182,7 +7178,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>0.71845790122767017</v>
+        <v>0.69782079781108441</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -7190,7 +7186,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>0.70302226646404042</v>
+        <v>0.70732749860489386</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -7198,7 +7194,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>0.67297028051984764</v>
+        <v>0.71020859042774487</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -7206,7 +7202,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>0.75547121090846114</v>
+        <v>0.73309801771687821</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -7214,7 +7210,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>0.76695518135067364</v>
+        <v>0.67108846340099026</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -7222,7 +7218,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>0.66461951134134634</v>
+        <v>0.65669551398357595</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
@@ -7230,7 +7226,7 @@
         <v>14</v>
       </c>
       <c r="B14">
-        <v>0.68873946854128576</v>
+        <v>0.68208576774013452</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
@@ -7238,7 +7234,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>0.68592596158651364</v>
+        <v>0.69385382805717488</v>
       </c>
     </row>
   </sheetData>
@@ -7253,10 +7249,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -7264,7 +7260,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>5446.2480795418742</v>
+        <v>4634.1609696816677</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -7272,7 +7268,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>3500.203597769294</v>
+        <v>2941.323507540254</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -7280,7 +7276,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>1657.757253843781</v>
+        <v>1286.695958306794</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -7288,7 +7284,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>1172.5252155386499</v>
+        <v>879.26261034195011</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -7296,7 +7292,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>915.80213061075631</v>
+        <v>710.71136086826493</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -7304,7 +7300,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>723.13324513893508</v>
+        <v>554.49241847272992</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -7312,7 +7308,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>518.85865662873471</v>
+        <v>393.91972221326722</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -7320,7 +7316,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>406.05628406026511</v>
+        <v>239.22870440074169</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -7328,7 +7324,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>302.13085726950368</v>
+        <v>200.15806615985039</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -7336,7 +7332,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>289.75586506184328</v>
+        <v>141.48818724150269</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -7344,7 +7340,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>97.647518564403555</v>
+        <v>117.9293352605082</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -7352,7 +7348,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>132.15973287166989</v>
+        <v>105.3759109983591</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
@@ -7360,7 +7356,7 @@
         <v>14</v>
       </c>
       <c r="B14">
-        <v>126.4486430818569</v>
+        <v>99.655317571092681</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
@@ -7368,7 +7364,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>68.037778343572597</v>
+        <v>59.391042282702607</v>
       </c>
     </row>
   </sheetData>
